--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484594_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484594_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V. MAS VIDAL</t>
+          <t>N. RAMON ANIBARRO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.186</v>
+        <v>6.8221</v>
       </c>
       <c r="E2" t="n">
-        <v>4.773</v>
+        <v>4.4229</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4131</v>
+        <v>2.3991</v>
       </c>
       <c r="G2" t="n">
-        <v>3.9796</v>
+        <v>2.7105</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1368</v>
+        <v>1.0021</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8427</v>
+        <v>1.7083</v>
       </c>
       <c r="J2" t="n">
-        <v>2.791</v>
+        <v>2.0256</v>
       </c>
       <c r="K2" t="n">
-        <v>2.7494</v>
+        <v>0.7337</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0417</v>
+        <v>1.2919</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1885</v>
+        <v>0.6849</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3875</v>
+        <v>0.2685</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8011</v>
+        <v>0.4164</v>
       </c>
       <c r="P2" t="n">
-        <v>2.0158</v>
+        <v>1.4661</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.0995</v>
       </c>
       <c r="R2" t="n">
-        <v>3.1154</v>
+        <v>2.5656</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4428</v>
+        <v>-0.5219</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5475</v>
+        <v>0.0076</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9903999999999999</v>
+        <v>-0.5294</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6335</v>
+        <v>3.1674</v>
       </c>
       <c r="W2" t="n">
-        <v>2.5339</v>
+        <v>3.4894</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.9005</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. RAMON ANIBARRO</t>
+          <t>V. MAS VIDAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.6946</v>
+        <v>5.906</v>
       </c>
       <c r="E3" t="n">
-        <v>3.791</v>
+        <v>4.4434</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9037</v>
+        <v>1.4626</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7105</v>
+        <v>3.9796</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0021</v>
+        <v>3.1368</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7083</v>
+        <v>0.8427</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0256</v>
+        <v>2.791</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7337</v>
+        <v>2.7494</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2919</v>
+        <v>0.0417</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6849</v>
+        <v>1.1885</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2685</v>
+        <v>0.3875</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4164</v>
+        <v>0.8011</v>
       </c>
       <c r="P3" t="n">
-        <v>1.4661</v>
+        <v>2.0158</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.0995</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5656</v>
+        <v>3.1154</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.6493</v>
+        <v>-0.7229</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6244</v>
+        <v>0.218</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.0249</v>
+        <v>-0.9408</v>
       </c>
       <c r="V3" t="n">
-        <v>3.1674</v>
+        <v>0.6335</v>
       </c>
       <c r="W3" t="n">
-        <v>3.4894</v>
+        <v>2.5339</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3219</v>
+        <v>-1.9005</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. VIDAL BALDOVI</t>
+          <t>A. VILLALBA MOLLA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0601</v>
+        <v>1.5358</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3708</v>
+        <v>1.54</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3107</v>
+        <v>-0.0041</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9763</v>
+        <v>0.9538</v>
       </c>
       <c r="H4" t="n">
-        <v>2.0631</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0868</v>
+        <v>0.2981</v>
       </c>
       <c r="J4" t="n">
-        <v>3.729</v>
+        <v>1.0912</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6873</v>
+        <v>1.0496</v>
       </c>
       <c r="L4" t="n">
         <v>0.0417</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.7526</v>
+        <v>-0.1374</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.6241</v>
+        <v>-0.3938</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1285</v>
+        <v>0.2564</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.4661</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2828</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1833</v>
+        <v>0.582</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3907</v>
+        <v>0.4487</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7926</v>
+        <v>0.1333</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6335</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. VILLALBA MOLLA</t>
+          <t>L. HYLLA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7915</v>
+        <v>1.5197</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6222</v>
+        <v>-2.1083</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1693</v>
+        <v>3.6281</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9538</v>
+        <v>0.5168</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6556999999999999</v>
+        <v>0.2509</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2981</v>
+        <v>0.266</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0912</v>
+        <v>-1.6121</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0496</v>
+        <v>-1.0128</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0417</v>
+        <v>-0.5994</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1374</v>
+        <v>2.129</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3938</v>
+        <v>1.2637</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2564</v>
+        <v>0.8653</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.0158</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.1833</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.1991</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8376</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5309</v>
+        <v>-0.313</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3067</v>
+        <v>-0.378</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. GARCIA SAHUQUILLO</t>
+          <t>S. VIDAL BALDOVI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4113</v>
+        <v>0.8807</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2167</v>
+        <v>1.7116</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.8054</v>
+        <v>-0.8309</v>
       </c>
       <c r="G6" t="n">
-        <v>3.0226</v>
+        <v>1.9763</v>
       </c>
       <c r="H6" t="n">
-        <v>1.9069</v>
+        <v>2.0631</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1157</v>
+        <v>-0.0868</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0963</v>
+        <v>3.729</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4614</v>
+        <v>3.6873</v>
       </c>
       <c r="L6" t="n">
-        <v>0.635</v>
+        <v>0.0417</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9262</v>
+        <v>-1.7526</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4456</v>
+        <v>-1.6241</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4807</v>
+        <v>-0.1285</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3665</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0158</v>
+        <v>-2.7489</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6493</v>
+        <v>1.2828</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5903</v>
+        <v>1.0039</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8484</v>
+        <v>0.7315</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2581</v>
+        <v>0.2724</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.8351</v>
+        <v>-0.6335</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2878</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-4.1229</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. HYLLA</t>
+          <t>B. BREM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1544</v>
+        <v>0.6726</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.548</v>
+        <v>0.3265</v>
       </c>
       <c r="F7" t="n">
-        <v>3.7024</v>
+        <v>0.3461</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5168</v>
+        <v>-0.5323</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2509</v>
+        <v>0.2274</v>
       </c>
       <c r="I7" t="n">
-        <v>0.266</v>
+        <v>-0.7597</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.6121</v>
+        <v>-0.0483</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.0128</v>
+        <v>1.1921</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5994</v>
+        <v>-1.2404</v>
       </c>
       <c r="M7" t="n">
-        <v>2.129</v>
+        <v>-0.484</v>
       </c>
       <c r="N7" t="n">
-        <v>1.2637</v>
+        <v>-0.9647</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8653</v>
+        <v>0.4807</v>
       </c>
       <c r="P7" t="n">
-        <v>2.0158</v>
+        <v>0.5498</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1833</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1991</v>
+        <v>0.5498</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0563</v>
+        <v>0.6552</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7526</v>
+        <v>0.3748</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3037</v>
+        <v>0.2803</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1533</v>
+        <v>0.079</v>
       </c>
       <c r="E8" t="n">
         <v>-0.0451</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1984</v>
+        <v>0.1241</v>
       </c>
       <c r="G8" t="n">
         <v>0.4404</v>
@@ -1078,13 +1078,13 @@
         <v>0.3665</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6536</v>
+        <v>-0.7279</v>
       </c>
       <c r="T8" t="n">
         <v>-0.1101</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5435</v>
+        <v>-0.6178</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. BREM</t>
+          <t>C. GARCIA SAHUQUILLO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1383</v>
+        <v>0.0322</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3605</v>
+        <v>2.0357</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2222</v>
+        <v>-2.0036</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5323</v>
+        <v>3.0226</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2274</v>
+        <v>1.9069</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7597</v>
+        <v>1.1157</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0483</v>
+        <v>2.0963</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1921</v>
+        <v>1.4614</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2404</v>
+        <v>0.635</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.484</v>
+        <v>0.9262</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9647</v>
+        <v>0.4456</v>
       </c>
       <c r="O9" t="n">
         <v>0.4807</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5498</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.0158</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5498</v>
+        <v>1.6493</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1557</v>
+        <v>0.2112</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3122</v>
+        <v>0.6674</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1565</v>
+        <v>-0.4563</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-2.8351</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.2878</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-4.1229</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.547</v>
+        <v>-0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2484</v>
+        <v>-1.6575</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7014</v>
+        <v>1.5775</v>
       </c>
       <c r="G10" t="n">
         <v>0.5137</v>
@@ -1234,13 +1234,13 @@
         <v>1.6493</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5947</v>
+        <v>-0.1276</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6425</v>
+        <v>-0.0516</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0479</v>
+        <v>-0.076</v>
       </c>
       <c r="V10" t="n">
         <v>0.6335</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3198</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.6058</v>
+        <v>-2.8776</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2859</v>
+        <v>2.7814</v>
       </c>
       <c r="G11" t="n">
         <v>2.2609</v>
@@ -1312,13 +1312,13 @@
         <v>3.1154</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.2534</v>
+        <v>-1.0298</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7896</v>
+        <v>-0.0614</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.4638</v>
+        <v>-0.9684</v>
       </c>
       <c r="V11" t="n">
         <v>0.3219</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>16.4461</v>
+        <v>17.2719</v>
       </c>
       <c r="E12" t="n">
-        <v>6.9659</v>
+        <v>7.791599999999998</v>
       </c>
       <c r="F12" t="n">
         <v>9.4803</v>
@@ -1369,13 +1369,13 @@
         <v>13.2347</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.9608000000000001</v>
+        <v>-0.9607999999999999</v>
       </c>
       <c r="M12" t="n">
         <v>3.5686</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9167999999999998</v>
+        <v>-0.9168000000000001</v>
       </c>
       <c r="O12" t="n">
         <v>4.4856</v>
@@ -1390,22 +1390,22 @@
         <v>16.4932</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.194599999999999</v>
+        <v>-1.3688</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0861</v>
+        <v>1.9119</v>
       </c>
       <c r="U12" t="n">
         <v>-3.2807</v>
       </c>
       <c r="V12" t="n">
-        <v>0.9658000000000007</v>
+        <v>0.9658000000000002</v>
       </c>
       <c r="W12" t="n">
         <v>8.266499999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.3007</v>
+        <v>-7.300699999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.1028</v>
+        <v>2.0912</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1257</v>
+        <v>2.8372</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0229</v>
+        <v>-0.746</v>
       </c>
       <c r="G13" t="n">
         <v>2.5783</v>
@@ -1468,13 +1468,13 @@
         <v>1.8326</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0614</v>
+        <v>0.0498</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5845</v>
+        <v>0.296</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5231</v>
+        <v>-0.2462</v>
       </c>
       <c r="V13" t="n">
         <v>2.212</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1845</v>
+        <v>0.9426</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4494</v>
+        <v>1.2571</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2649</v>
+        <v>-0.3144</v>
       </c>
       <c r="G14" t="n">
         <v>1.8065</v>
@@ -1546,13 +1546,13 @@
         <v>1.2828</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4617</v>
+        <v>0.2198</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7315</v>
+        <v>0.5392</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2698</v>
+        <v>-0.3194</v>
       </c>
       <c r="V14" t="n">
         <v>-1.267</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. PARDO GALLENT</t>
+          <t>J. SÁEZ GONZÁLEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,40 +1579,40 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.514</v>
+        <v>0.3251</v>
       </c>
       <c r="E15" t="n">
-        <v>0.586</v>
+        <v>0.3251</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.07199999999999999</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.7296</v>
+        <v>0.3251</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8578</v>
+        <v>0.3251</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1282</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.641</v>
+        <v>0.3251</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.641</v>
+        <v>0.3251</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0885</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2167</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1282</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1624,13 +1624,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2435</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.227</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0165</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. SÁEZ GONZÁLEZ</t>
+          <t>G. PARDO GALLENT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,40 +1657,40 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3251</v>
+        <v>-0.1344</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3251</v>
+        <v>-0.0871</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-0.0472</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3251</v>
+        <v>-0.7296</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3251</v>
+        <v>-0.8578</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.1282</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3251</v>
+        <v>-0.641</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3251</v>
+        <v>-0.641</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>-0.0885</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-0.2167</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>0.1282</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1702,13 +1702,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>0.5952</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.0413</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9227</v>
+        <v>-0.3458</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3086</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="F17" t="n">
         <v>-1.2313</v>
@@ -1780,10 +1780,10 @@
         <v>1.4661</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4947</v>
+        <v>0.0822</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6976</v>
+        <v>-0.1206</v>
       </c>
       <c r="U17" t="n">
         <v>0.2029</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. VERGARA APARICIO</t>
+          <t>X. CORTINA CAMPOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9917</v>
+        <v>-1.4744</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3455</v>
+        <v>-1.8407</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3371</v>
+        <v>0.3663</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.2304</v>
+        <v>-1.8403</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.1024</v>
+        <v>-1.3692</v>
       </c>
       <c r="I18" t="n">
-        <v>0.872</v>
+        <v>-0.4711</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1999</v>
+        <v>-0.6985</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.576</v>
+        <v>-0.0992</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7759</v>
+        <v>-0.5994</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4303</v>
+        <v>-1.1418</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.5264</v>
+        <v>-1.27</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0961</v>
+        <v>0.1282</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5498</v>
+        <v>-0.733</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.0158</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5498</v>
+        <v>1.2828</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3225</v>
+        <v>1.099</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1456</v>
+        <v>0.8737</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1769</v>
+        <v>0.2253</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6335</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X. CORTINA CAMPOS</t>
+          <t>J. VERGARA APARICIO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3039</v>
+        <v>-1.5249</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7445</v>
+        <v>-0.0392</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4406</v>
+        <v>-1.4858</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.8403</v>
+        <v>-1.2304</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3692</v>
+        <v>-2.1024</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4711</v>
+        <v>0.872</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6985</v>
+        <v>0.1999</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.0992</v>
+        <v>-0.576</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5994</v>
+        <v>0.7759</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1418</v>
+        <v>-1.4303</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.27</v>
+        <v>-1.5264</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1282</v>
+        <v>0.0961</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.733</v>
+        <v>0.5498</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0158</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2828</v>
+        <v>0.5498</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2695</v>
+        <v>-0.2108</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9698</v>
+        <v>-0.2391</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2996</v>
+        <v>0.0283</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.6335</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. ALMONACID RUBIO</t>
+          <t>P. PAREJA ANDRES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2203</v>
+        <v>-2.0581</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4685</v>
+        <v>-2.3925</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7518</v>
+        <v>0.3344</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.9395</v>
+        <v>-2.3826</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1829</v>
+        <v>-3.4693</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.7566</v>
+        <v>1.0867</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.2859</v>
+        <v>-1.0713</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7218</v>
+        <v>-1.8055</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.5641</v>
+        <v>0.7342</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6535</v>
+        <v>-1.3113</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4611</v>
+        <v>-1.6638</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1925</v>
+        <v>0.3525</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1833</v>
+        <v>0.3665</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.0995</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2828</v>
+        <v>1.4661</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5805</v>
+        <v>-0.042</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6946</v>
+        <v>-0.2217</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1141</v>
+        <v>0.1797</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.2224</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. TORREGROSA ROCA</t>
+          <t>A. ALMONACID RUBIO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2972</v>
+        <v>-2.1139</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8888</v>
+        <v>-1.5646</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4084</v>
+        <v>-0.5493</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.9018</v>
+        <v>-3.9395</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.86</v>
+        <v>-1.1829</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.0417</v>
+        <v>-2.7566</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.3737</v>
+        <v>-3.2859</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5077</v>
+        <v>-0.7218</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.8814</v>
+        <v>-2.5641</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5281</v>
+        <v>-0.6535</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3677</v>
+        <v>-0.4611</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1603</v>
+        <v>-0.1925</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9163</v>
+        <v>0.1833</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9163</v>
+        <v>-1.0995</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8326</v>
+        <v>1.2828</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0103</v>
+        <v>0.6868</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4012</v>
+        <v>0.5984</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.391</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3219</v>
+        <v>0.9554</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.2224</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.3219</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. SAEZ GONZALEZ</t>
+          <t>R. TORREGROSA ROCA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6484</v>
+        <v>-2.2301</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7269</v>
+        <v>-2.1772</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0785</v>
+        <v>-0.0529</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.524</v>
+        <v>-2.9018</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8508</v>
+        <v>-0.86</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6732</v>
+        <v>-2.0417</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7743</v>
+        <v>-1.3737</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1333</v>
+        <v>0.5077</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.641</v>
+        <v>-1.8814</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7496</v>
+        <v>-1.5281</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7175</v>
+        <v>-1.3677</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0321</v>
+        <v>-0.1603</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.2828</v>
+        <v>0.9163</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.7489</v>
+        <v>-0.9163</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4661</v>
+        <v>1.8326</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8023</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4744</v>
+        <v>0.1128</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3279</v>
+        <v>-0.0355</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6439</v>
+        <v>-0.3219</v>
       </c>
       <c r="W22" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.9658</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. PAREJA ANDRES</t>
+          <t>J. SAEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.129</v>
+        <v>-2.5902</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1618</v>
+        <v>-2.7269</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0328</v>
+        <v>0.1367</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.3826</v>
+        <v>-1.524</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.4693</v>
+        <v>-0.8508</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0867</v>
+        <v>-0.6732</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.0713</v>
+        <v>-0.7743</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.8055</v>
+        <v>-0.1333</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7342</v>
+        <v>-0.641</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3113</v>
+        <v>-0.7496</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.6638</v>
+        <v>-0.7175</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3525</v>
+        <v>-0.0321</v>
       </c>
       <c r="P23" t="n">
-        <v>0.3665</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0995</v>
+        <v>-2.7489</v>
       </c>
       <c r="R23" t="n">
         <v>1.4661</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1129</v>
+        <v>0.8605</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9909</v>
+        <v>0.4744</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.122</v>
+        <v>0.3861</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.9658</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.393</v>
+        <v>-2.6311</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.5495</v>
+        <v>-3.0687</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1565</v>
+        <v>0.4376</v>
       </c>
       <c r="G24" t="n">
         <v>-5.2104</v>
@@ -2326,13 +2326,13 @@
         <v>1.8326</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4051</v>
+        <v>0.3569</v>
       </c>
       <c r="T24" t="n">
-        <v>0.126</v>
+        <v>0.6067</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.531</v>
+        <v>-0.2498</v>
       </c>
       <c r="V24" t="n">
         <v>2.2224</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.6665</v>
+        <v>-3.4203</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.0807</v>
+        <v>-0.8884</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.5858</v>
+        <v>-2.5319</v>
       </c>
       <c r="G25" t="n">
         <v>-1.3055</v>
@@ -2404,13 +2404,13 @@
         <v>0.3665</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5443</v>
+        <v>-0.2981</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3854</v>
+        <v>-0.1931</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1589</v>
+        <v>-0.105</v>
       </c>
       <c r="V25" t="n">
         <v>-1.267</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-16.4463</v>
+        <v>-15.1643</v>
       </c>
       <c r="E26" t="n">
-        <v>-9.480399999999999</v>
+        <v>-9.480300000000002</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.9658</v>
+        <v>-5.6838</v>
       </c>
       <c r="G26" t="n">
         <v>-15.8426</v>
@@ -2482,13 +2482,13 @@
         <v>14.6608</v>
       </c>
       <c r="S26" t="n">
-        <v>2.1947</v>
+        <v>3.4766</v>
       </c>
       <c r="T26" t="n">
-        <v>3.2807</v>
+        <v>3.2806</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.0861</v>
+        <v>0.1960999999999999</v>
       </c>
       <c r="V26" t="n">
         <v>-0.9659</v>
@@ -2497,7 +2497,7 @@
         <v>7.300599999999999</v>
       </c>
       <c r="X26" t="n">
-        <v>-8.266499999999999</v>
+        <v>-8.266500000000001</v>
       </c>
     </row>
   </sheetData>
